--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-fvc.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-fvc.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$185</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7238" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6939" uniqueCount="707">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01</t>
+    <t>2026-09-02</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1797,237 +1797,210 @@
     <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
+    <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
+  </si>
+  <si>
+    <t>Observation.component.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Why the component result is missing</t>
+  </si>
+  <si>
+    <t>Provides a reason why the expected value in the element Observation.component.value[x] is missing.</t>
+  </si>
+  <si>
+    <t>"Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
+  </si>
+  <si>
+    <t>Observation.component.interpretation</t>
+  </si>
+  <si>
+    <t>High, low, normal, etc.</t>
+  </si>
+  <si>
+    <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
+  </si>
+  <si>
+    <t>Observation.component.referenceRange</t>
+  </si>
+  <si>
+    <t>Provides guide for interpretation of component result</t>
+  </si>
+  <si>
+    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted</t>
+  </si>
+  <si>
+    <t>predicted</t>
+  </si>
+  <si>
+    <t>Vorhersage</t>
+  </si>
+  <si>
+    <t>vorhergesagtes Messergebnis</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.id</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.id</t>
+  </si>
+  <si>
+    <t>Observation.component.code.id</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:sct</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:sct.id</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:sct.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:sct.system</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.system</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:sct.version</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:sct.code</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:sct.display</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:sct.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:loinc</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:loinc.id</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:loinc.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:loinc.system</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:loinc.version</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:loinc.code</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:loinc.display</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:loinc.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.text</t>
+  </si>
+  <si>
+    <t>Observation.component.code.text</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.value[x]</t>
+  </si>
+  <si>
     <t xml:space="preserve">type:$this}
 </t>
   </si>
   <si>
-    <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity</t>
   </si>
   <si>
     <t>valueQuantity</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.id</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity.id</t>
   </si>
   <si>
     <t>Observation.component.value[x].id</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.extension</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity.extension</t>
   </si>
   <si>
     <t>Observation.component.value[x].extension</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.value</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity.value</t>
   </si>
   <si>
     <t>Observation.component.value[x].value</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.comparator</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity.comparator</t>
   </si>
   <si>
     <t>Observation.component.value[x].comparator</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.unit</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity.unit</t>
   </si>
   <si>
     <t>Observation.component.value[x].unit</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.system</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity.system</t>
   </si>
   <si>
     <t>Observation.component.value[x].system</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.code</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity.code</t>
   </si>
   <si>
     <t>Observation.component.value[x].code</t>
-  </si>
-  <si>
-    <t>Observation.component.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Why the component result is missing</t>
-  </si>
-  <si>
-    <t>Provides a reason why the expected value in the element Observation.component.value[x] is missing.</t>
-  </si>
-  <si>
-    <t>"Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
-The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
-  </si>
-  <si>
-    <t>Observation.component.interpretation</t>
-  </si>
-  <si>
-    <t>High, low, normal, etc.</t>
-  </si>
-  <si>
-    <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
-  </si>
-  <si>
-    <t>Observation.component.referenceRange</t>
-  </si>
-  <si>
-    <t>Provides guide for interpretation of component result</t>
-  </si>
-  <si>
-    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted</t>
-  </si>
-  <si>
-    <t>predicted</t>
-  </si>
-  <si>
-    <t>Vorhersage</t>
-  </si>
-  <si>
-    <t>vorhergesagtes Messergebnis</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.id</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.id</t>
-  </si>
-  <si>
-    <t>Observation.component.code.id</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.extension</t>
-  </si>
-  <si>
-    <t>Observation.component.code.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.id</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.extension</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.system</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.version</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.code</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.display</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.id</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.system</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.version</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.code</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.display</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.text</t>
-  </si>
-  <si>
-    <t>Observation.component.code.text</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.id</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.value</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.comparator</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.unit</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.system</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.code</t>
   </si>
   <si>
     <t>Observation.component:predicted.dataAbsentReason</t>
@@ -2556,7 +2529,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO193"/>
+  <dimension ref="A1:AO185"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.09765625" customWidth="true" bestFit="true"/>
@@ -12780,14 +12753,16 @@
         <v>81</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AC87" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>565</v>
@@ -12808,7 +12783,7 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>391</v>
@@ -12822,14 +12797,12 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>573</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>81</v>
       </c>
@@ -12847,22 +12820,22 @@
         <v>81</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>384</v>
+        <v>232</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
@@ -12887,13 +12860,13 @@
         <v>81</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -12911,7 +12884,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12920,7 +12893,7 @@
         <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>103</v>
@@ -12929,35 +12902,35 @@
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>571</v>
+        <v>81</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>575</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>81</v>
@@ -12969,16 +12942,20 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>106</v>
+        <v>576</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
       </c>
@@ -13002,13 +12979,13 @@
         <v>81</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>81</v>
@@ -13026,46 +13003,46 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>108</v>
+        <v>575</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>81</v>
+        <v>450</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>81</v>
+        <v>451</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13084,18 +13061,20 @@
         <v>81</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>112</v>
+        <v>579</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>113</v>
+        <v>580</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>496</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>497</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
       </c>
@@ -13131,19 +13110,19 @@
         <v>81</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>118</v>
+        <v>578</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13155,7 +13134,7 @@
         <v>81</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>81</v>
@@ -13164,7 +13143,7 @@
         <v>81</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>81</v>
+        <v>499</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>81</v>
@@ -13175,12 +13154,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="C91" s="2"/>
+        <v>551</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>582</v>
+      </c>
       <c r="D91" t="s" s="2">
         <v>81</v>
       </c>
@@ -13201,19 +13182,19 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>396</v>
+        <v>493</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>397</v>
+        <v>583</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>398</v>
+        <v>584</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>399</v>
+        <v>554</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>400</v>
+        <v>555</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -13262,13 +13243,13 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>401</v>
+        <v>551</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>81</v>
@@ -13283,7 +13264,7 @@
         <v>81</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>402</v>
+        <v>556</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
@@ -13294,10 +13275,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>581</v>
+        <v>557</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13314,30 +13295,26 @@
         <v>81</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>404</v>
+        <v>106</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>405</v>
+        <v>107</v>
       </c>
       <c r="N92" s="2"/>
-      <c r="O92" t="s" s="2">
-        <v>406</v>
-      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q92" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
         <v>81</v>
       </c>
@@ -13357,13 +13334,13 @@
         <v>81</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>408</v>
+        <v>81</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>409</v>
+        <v>81</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>81</v>
@@ -13381,7 +13358,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>410</v>
+        <v>108</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13393,7 +13370,7 @@
         <v>81</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>81</v>
@@ -13402,7 +13379,7 @@
         <v>81</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>81</v>
@@ -13411,46 +13388,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>583</v>
+        <v>558</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>413</v>
+        <v>112</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>81</v>
       </c>
@@ -13498,19 +13475,19 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>417</v>
+        <v>118</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>81</v>
@@ -13519,7 +13496,7 @@
         <v>81</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>81</v>
@@ -13528,45 +13505,47 @@
         <v>81</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>585</v>
+        <v>559</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>81</v>
+        <v>503</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I94" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="J94" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>420</v>
+        <v>504</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>505</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O94" t="s" s="2">
-        <v>422</v>
+        <v>194</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -13615,19 +13594,19 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>424</v>
+        <v>506</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>81</v>
@@ -13636,7 +13615,7 @@
         <v>81</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>81</v>
@@ -13645,12 +13624,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>587</v>
+        <v>560</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13658,13 +13637,13 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>81</v>
@@ -13673,19 +13652,19 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>427</v>
+        <v>561</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>428</v>
+        <v>562</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>429</v>
+        <v>563</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>430</v>
+        <v>261</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -13710,13 +13689,13 @@
         <v>81</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>81</v>
@@ -13734,10 +13713,10 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>431</v>
+        <v>560</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>91</v>
@@ -13752,13 +13731,13 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>81</v>
+        <v>564</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>418</v>
+        <v>266</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>81</v>
@@ -13766,10 +13745,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13792,20 +13771,16 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>589</v>
+        <v>106</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>81</v>
       </c>
@@ -13829,13 +13804,13 @@
         <v>81</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>81</v>
@@ -13853,7 +13828,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>588</v>
+        <v>108</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13862,10 +13837,10 @@
         <v>91</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>439</v>
+        <v>81</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>81</v>
@@ -13874,7 +13849,7 @@
         <v>81</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>81</v>
@@ -13885,14 +13860,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>592</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>442</v>
+        <v>110</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13911,20 +13886,18 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>593</v>
+        <v>112</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>594</v>
+        <v>113</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>81</v>
       </c>
@@ -13948,31 +13921,31 @@
         <v>81</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>592</v>
+        <v>118</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13984,30 +13957,30 @@
         <v>81</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>449</v>
+        <v>81</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>450</v>
+        <v>81</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14027,22 +14000,22 @@
         <v>81</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>596</v>
+        <v>243</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>597</v>
+        <v>244</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>496</v>
+        <v>245</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>497</v>
+        <v>246</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>81</v>
@@ -14079,19 +14052,17 @@
         <v>81</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="AC98" s="2"/>
       <c r="AD98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>595</v>
+        <v>248</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -14112,7 +14083,7 @@
         <v>81</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>499</v>
+        <v>249</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>81</v>
@@ -14123,13 +14094,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>551</v>
+        <v>594</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>599</v>
+        <v>274</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>81</v>
@@ -14151,19 +14122,19 @@
         <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>493</v>
+        <v>144</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>600</v>
+        <v>275</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>601</v>
+        <v>276</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>554</v>
+        <v>245</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>555</v>
+        <v>246</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>81</v>
@@ -14188,13 +14159,11 @@
         <v>81</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>81</v>
+        <v>277</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>81</v>
@@ -14212,7 +14181,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>551</v>
+        <v>248</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14233,7 +14202,7 @@
         <v>81</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>556</v>
+        <v>249</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>81</v>
@@ -14244,10 +14213,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>557</v>
+        <v>597</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14359,10 +14328,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>558</v>
+        <v>599</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14432,16 +14401,16 @@
         <v>81</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>118</v>
@@ -14476,45 +14445,45 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>559</v>
+        <v>601</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>503</v>
+        <v>81</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J102" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>504</v>
+        <v>284</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>505</v>
+        <v>285</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>114</v>
+        <v>286</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>194</v>
+        <v>287</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>81</v>
@@ -14563,19 +14532,19 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>506</v>
+        <v>288</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>81</v>
@@ -14584,7 +14553,7 @@
         <v>81</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>81</v>
+        <v>289</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>81</v>
@@ -14595,10 +14564,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>560</v>
+        <v>603</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14606,7 +14575,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>91</v>
@@ -14621,20 +14590,18 @@
         <v>92</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>561</v>
+        <v>292</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>562</v>
+        <v>293</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>81</v>
       </c>
@@ -14658,13 +14625,13 @@
         <v>81</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>81</v>
@@ -14682,10 +14649,10 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>560</v>
+        <v>295</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>91</v>
@@ -14700,13 +14667,13 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>564</v>
+        <v>81</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>81</v>
@@ -14714,10 +14681,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14737,19 +14704,21 @@
         <v>81</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>106</v>
+        <v>299</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>107</v>
+        <v>300</v>
       </c>
       <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+      <c r="O104" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>81</v>
       </c>
@@ -14773,13 +14742,11 @@
         <v>81</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>81</v>
@@ -14797,7 +14764,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>108</v>
+        <v>303</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14809,7 +14776,7 @@
         <v>81</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>81</v>
@@ -14818,7 +14785,7 @@
         <v>81</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>81</v>
+        <v>304</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>81</v>
@@ -14829,21 +14796,21 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>81</v>
@@ -14852,21 +14819,21 @@
         <v>81</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>112</v>
+        <v>307</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O105" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>81</v>
       </c>
@@ -14902,31 +14869,31 @@
         <v>81</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>118</v>
+        <v>310</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>81</v>
@@ -14935,7 +14902,7 @@
         <v>81</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>81</v>
+        <v>311</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>81</v>
@@ -14946,10 +14913,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14960,7 +14927,7 @@
         <v>79</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>81</v>
@@ -14972,19 +14939,19 @@
         <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>144</v>
+        <v>314</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>243</v>
+        <v>315</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>244</v>
+        <v>316</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>245</v>
+        <v>317</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>246</v>
+        <v>318</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>81</v>
@@ -15021,23 +14988,25 @@
         <v>81</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AC106" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>248</v>
+        <v>319</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>81</v>
@@ -15052,7 +15021,7 @@
         <v>81</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>249</v>
+        <v>320</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>81</v>
@@ -15063,13 +15032,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>611</v>
+        <v>594</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>274</v>
+        <v>322</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>81</v>
@@ -15094,10 +15063,10 @@
         <v>144</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>275</v>
+        <v>323</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>276</v>
+        <v>324</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>245</v>
@@ -15132,7 +15101,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>277</v>
+        <v>325</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>81</v>
@@ -15182,10 +15151,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>614</v>
+        <v>597</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15297,10 +15266,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15414,10 +15383,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>618</v>
+        <v>601</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15533,10 +15502,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15650,10 +15619,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>622</v>
+        <v>605</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15715,7 +15684,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>81</v>
@@ -15765,10 +15734,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>624</v>
+        <v>607</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15882,10 +15851,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>626</v>
+        <v>609</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15999,16 +15968,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="C115" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>619</v>
+      </c>
+      <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>81</v>
       </c>
@@ -16020,7 +15987,7 @@
         <v>91</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>81</v>
@@ -16029,19 +15996,19 @@
         <v>92</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>323</v>
+        <v>251</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>324</v>
+        <v>252</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>81</v>
@@ -16066,11 +16033,13 @@
         <v>81</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y115" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z115" t="s" s="2">
-        <v>325</v>
+        <v>81</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>81</v>
@@ -16088,13 +16057,13 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>81</v>
@@ -16109,7 +16078,7 @@
         <v>81</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>81</v>
@@ -16120,10 +16089,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>614</v>
+        <v>565</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16143,19 +16112,23 @@
         <v>81</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>105</v>
+        <v>566</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>106</v>
+        <v>567</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>81</v>
       </c>
@@ -16191,19 +16164,17 @@
         <v>81</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="AC116" s="2"/>
       <c r="AD116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>108</v>
+        <v>565</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16215,41 +16186,43 @@
         <v>81</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>81</v>
+        <v>570</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="C117" s="2"/>
+        <v>565</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>623</v>
+      </c>
       <c r="D117" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>81</v>
@@ -16258,21 +16231,23 @@
         <v>81</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>111</v>
+        <v>384</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>112</v>
+        <v>567</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>113</v>
+        <v>568</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O117" s="2"/>
+        <v>569</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>81</v>
       </c>
@@ -16308,54 +16283,54 @@
         <v>81</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC117" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE117" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>118</v>
+        <v>565</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>81</v>
+        <v>570</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16375,23 +16350,19 @@
         <v>81</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>284</v>
+        <v>106</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>81</v>
       </c>
@@ -16439,7 +16410,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>288</v>
+        <v>108</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16451,7 +16422,7 @@
         <v>81</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>81</v>
@@ -16460,7 +16431,7 @@
         <v>81</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>81</v>
@@ -16471,21 +16442,21 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>81</v>
@@ -16494,19 +16465,19 @@
         <v>81</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>292</v>
+        <v>112</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>293</v>
+        <v>113</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>294</v>
+        <v>114</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16544,31 +16515,31 @@
         <v>81</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC119" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE119" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>295</v>
+        <v>118</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>81</v>
@@ -16577,7 +16548,7 @@
         <v>81</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>296</v>
+        <v>81</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>81</v>
@@ -16586,12 +16557,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="120" hidden="true">
+    <row r="120">
       <c r="A120" t="s" s="2">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16605,7 +16576,7 @@
         <v>91</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>81</v>
@@ -16614,17 +16585,19 @@
         <v>92</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>166</v>
+        <v>396</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>299</v>
+        <v>397</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N120" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="O120" t="s" s="2">
-        <v>301</v>
+        <v>400</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>81</v>
@@ -16649,11 +16622,13 @@
         <v>81</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y120" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z120" t="s" s="2">
-        <v>331</v>
+        <v>81</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>81</v>
@@ -16671,7 +16646,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>303</v>
+        <v>401</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16692,7 +16667,7 @@
         <v>81</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>304</v>
+        <v>402</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>81</v>
@@ -16703,10 +16678,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16723,28 +16698,30 @@
         <v>81</v>
       </c>
       <c r="I121" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J121" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>307</v>
+        <v>404</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>308</v>
+        <v>405</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>309</v>
+        <v>406</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q121" s="2"/>
+      <c r="Q121" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="R121" t="s" s="2">
         <v>81</v>
       </c>
@@ -16764,13 +16741,13 @@
         <v>81</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>81</v>
+        <v>408</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>81</v>
+        <v>409</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>81</v>
@@ -16788,7 +16765,7 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>310</v>
+        <v>410</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16809,7 +16786,7 @@
         <v>81</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>311</v>
+        <v>411</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>81</v>
@@ -16818,12 +16795,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="122" hidden="true">
+    <row r="122">
       <c r="A122" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16837,7 +16814,7 @@
         <v>91</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>81</v>
@@ -16846,19 +16823,17 @@
         <v>92</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>314</v>
+        <v>105</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>315</v>
+        <v>413</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>318</v>
+        <v>415</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>81</v>
@@ -16868,7 +16843,7 @@
         <v>81</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>81</v>
@@ -16907,7 +16882,7 @@
         <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>319</v>
+        <v>417</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16928,7 +16903,7 @@
         <v>81</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>320</v>
+        <v>418</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>81</v>
@@ -16937,12 +16912,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="123" hidden="true">
+    <row r="123">
       <c r="A123" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B123" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16956,7 +16931,7 @@
         <v>91</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>81</v>
@@ -16965,19 +16940,17 @@
         <v>92</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>251</v>
+        <v>420</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>254</v>
+        <v>422</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>81</v>
@@ -16987,7 +16960,7 @@
         <v>81</v>
       </c>
       <c r="S123" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="T123" t="s" s="2">
         <v>81</v>
@@ -17026,7 +16999,7 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>255</v>
+        <v>424</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -17035,7 +17008,7 @@
         <v>91</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>81</v>
+        <v>425</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>103</v>
@@ -17047,7 +17020,7 @@
         <v>81</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>256</v>
+        <v>418</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>81</v>
@@ -17056,12 +17029,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="B124" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17075,7 +17048,7 @@
         <v>91</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>81</v>
@@ -17084,19 +17057,19 @@
         <v>92</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>566</v>
+        <v>166</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>567</v>
+        <v>427</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>568</v>
+        <v>428</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>569</v>
+        <v>429</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>388</v>
+        <v>430</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>81</v>
@@ -17106,7 +17079,7 @@
         <v>81</v>
       </c>
       <c r="S124" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="T124" t="s" s="2">
         <v>81</v>
@@ -17133,17 +17106,19 @@
         <v>81</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AC124" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>638</v>
+        <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>565</v>
+        <v>431</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17161,28 +17136,26 @@
         <v>81</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>571</v>
+        <v>81</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="C125" t="s" s="2">
-        <v>573</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
         <v>81</v>
       </c>
@@ -17200,22 +17173,22 @@
         <v>81</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>384</v>
+        <v>232</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>81</v>
@@ -17240,13 +17213,13 @@
         <v>81</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>81</v>
@@ -17264,7 +17237,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17273,7 +17246,7 @@
         <v>91</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>103</v>
@@ -17282,35 +17255,35 @@
         <v>81</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>571</v>
+        <v>81</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>575</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>81</v>
@@ -17322,16 +17295,20 @@
         <v>81</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>106</v>
+        <v>576</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>81</v>
       </c>
@@ -17355,13 +17332,13 @@
         <v>81</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>81</v>
@@ -17379,46 +17356,46 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>108</v>
+        <v>575</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>81</v>
+        <v>450</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>81</v>
+        <v>451</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
@@ -17437,18 +17414,20 @@
         <v>81</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>112</v>
+        <v>579</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>113</v>
+        <v>580</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O127" s="2"/>
+        <v>496</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>497</v>
+      </c>
       <c r="P127" t="s" s="2">
         <v>81</v>
       </c>
@@ -17484,19 +17463,19 @@
         <v>81</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC127" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD127" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE127" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>118</v>
+        <v>578</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17508,7 +17487,7 @@
         <v>81</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>81</v>
@@ -17517,7 +17496,7 @@
         <v>81</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>81</v>
+        <v>499</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>81</v>
@@ -17526,14 +17505,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="128" hidden="true">
+    <row r="128">
       <c r="A128" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="C128" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="B128" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
         <v>81</v>
       </c>
@@ -17545,7 +17526,7 @@
         <v>91</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>81</v>
@@ -17554,19 +17535,19 @@
         <v>92</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>396</v>
+        <v>493</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>397</v>
+        <v>643</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>398</v>
+        <v>644</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>399</v>
+        <v>554</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>400</v>
+        <v>555</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>81</v>
@@ -17615,13 +17596,13 @@
         <v>81</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>401</v>
+        <v>551</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>81</v>
@@ -17636,7 +17617,7 @@
         <v>81</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>402</v>
+        <v>556</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>81</v>
@@ -17647,10 +17628,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>581</v>
+        <v>557</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17667,30 +17648,26 @@
         <v>81</v>
       </c>
       <c r="I129" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>404</v>
+        <v>106</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>405</v>
+        <v>107</v>
       </c>
       <c r="N129" s="2"/>
-      <c r="O129" t="s" s="2">
-        <v>406</v>
-      </c>
+      <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q129" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="Q129" s="2"/>
       <c r="R129" t="s" s="2">
         <v>81</v>
       </c>
@@ -17710,13 +17687,13 @@
         <v>81</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>408</v>
+        <v>81</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>409</v>
+        <v>81</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>81</v>
@@ -17734,7 +17711,7 @@
         <v>81</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>410</v>
+        <v>108</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17746,7 +17723,7 @@
         <v>81</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>81</v>
@@ -17755,7 +17732,7 @@
         <v>81</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>81</v>
@@ -17766,21 +17743,21 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>583</v>
+        <v>558</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>81</v>
@@ -17789,21 +17766,21 @@
         <v>81</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>413</v>
+        <v>112</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N130" s="2"/>
-      <c r="O130" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>81</v>
       </c>
@@ -17812,7 +17789,7 @@
         <v>81</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>81</v>
@@ -17851,19 +17828,19 @@
         <v>81</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>417</v>
+        <v>118</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>81</v>
@@ -17872,7 +17849,7 @@
         <v>81</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>81</v>
@@ -17883,43 +17860,45 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>585</v>
+        <v>559</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>81</v>
+        <v>503</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J131" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>420</v>
+        <v>504</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N131" s="2"/>
+        <v>505</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O131" t="s" s="2">
-        <v>422</v>
+        <v>194</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>81</v>
@@ -17929,7 +17908,7 @@
         <v>81</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>81</v>
@@ -17968,19 +17947,19 @@
         <v>81</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>424</v>
+        <v>506</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>81</v>
@@ -17989,7 +17968,7 @@
         <v>81</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>81</v>
@@ -18000,10 +17979,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>587</v>
+        <v>560</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18011,7 +17990,7 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G132" t="s" s="2">
         <v>91</v>
@@ -18026,19 +18005,19 @@
         <v>92</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>427</v>
+        <v>561</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>428</v>
+        <v>562</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>429</v>
+        <v>563</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>430</v>
+        <v>261</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>81</v>
@@ -18048,7 +18027,7 @@
         <v>81</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>81</v>
@@ -18063,13 +18042,13 @@
         <v>81</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>81</v>
@@ -18087,10 +18066,10 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>431</v>
+        <v>560</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>91</v>
@@ -18105,13 +18084,13 @@
         <v>81</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>81</v>
+        <v>564</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>418</v>
+        <v>266</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>81</v>
@@ -18119,10 +18098,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18145,20 +18124,16 @@
         <v>81</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>589</v>
+        <v>106</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>81</v>
       </c>
@@ -18182,13 +18157,13 @@
         <v>81</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>81</v>
@@ -18206,7 +18181,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>588</v>
+        <v>108</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18215,10 +18190,10 @@
         <v>91</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>439</v>
+        <v>81</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>81</v>
@@ -18227,7 +18202,7 @@
         <v>81</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>81</v>
@@ -18238,14 +18213,14 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>592</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>442</v>
+        <v>110</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -18264,20 +18239,18 @@
         <v>81</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>593</v>
+        <v>112</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>594</v>
+        <v>113</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>81</v>
       </c>
@@ -18301,31 +18274,31 @@
         <v>81</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB134" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC134" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE134" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>592</v>
+        <v>118</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18337,30 +18310,30 @@
         <v>81</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>449</v>
+        <v>81</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>450</v>
+        <v>81</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18380,22 +18353,22 @@
         <v>81</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>596</v>
+        <v>243</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>597</v>
+        <v>244</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>496</v>
+        <v>245</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>497</v>
+        <v>246</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>81</v>
@@ -18432,19 +18405,17 @@
         <v>81</v>
       </c>
       <c r="AB135" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="AC135" s="2"/>
       <c r="AD135" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE135" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>595</v>
+        <v>248</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18465,7 +18436,7 @@
         <v>81</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>499</v>
+        <v>249</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>81</v>
@@ -18476,13 +18447,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>551</v>
+        <v>594</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>651</v>
+        <v>274</v>
       </c>
       <c r="D136" t="s" s="2">
         <v>81</v>
@@ -18504,19 +18475,19 @@
         <v>92</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>493</v>
+        <v>144</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>652</v>
+        <v>275</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>653</v>
+        <v>276</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>554</v>
+        <v>245</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>555</v>
+        <v>246</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>81</v>
@@ -18541,13 +18512,11 @@
         <v>81</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y136" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y136" s="2"/>
       <c r="Z136" t="s" s="2">
-        <v>81</v>
+        <v>277</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>81</v>
@@ -18565,7 +18534,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>551</v>
+        <v>248</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18586,7 +18555,7 @@
         <v>81</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>556</v>
+        <v>249</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>81</v>
@@ -18597,10 +18566,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>557</v>
+        <v>597</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18712,10 +18681,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>558</v>
+        <v>599</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18785,16 +18754,16 @@
         <v>81</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF138" t="s" s="2">
         <v>118</v>
@@ -18829,45 +18798,45 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>559</v>
+        <v>601</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>503</v>
+        <v>81</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I139" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J139" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>504</v>
+        <v>284</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>505</v>
+        <v>285</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>114</v>
+        <v>286</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>194</v>
+        <v>287</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>81</v>
@@ -18916,19 +18885,19 @@
         <v>81</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>506</v>
+        <v>288</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>81</v>
@@ -18937,7 +18906,7 @@
         <v>81</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>81</v>
+        <v>289</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>81</v>
@@ -18948,10 +18917,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>560</v>
+        <v>603</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18959,7 +18928,7 @@
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G140" t="s" s="2">
         <v>91</v>
@@ -18974,20 +18943,18 @@
         <v>92</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>561</v>
+        <v>292</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>562</v>
+        <v>293</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>81</v>
       </c>
@@ -19011,13 +18978,13 @@
         <v>81</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>81</v>
@@ -19035,10 +19002,10 @@
         <v>81</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>560</v>
+        <v>295</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH140" t="s" s="2">
         <v>91</v>
@@ -19053,13 +19020,13 @@
         <v>81</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>564</v>
+        <v>81</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>81</v>
@@ -19067,10 +19034,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19090,19 +19057,21 @@
         <v>81</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>106</v>
+        <v>299</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>107</v>
+        <v>300</v>
       </c>
       <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
+      <c r="O141" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>81</v>
       </c>
@@ -19126,13 +19095,11 @@
         <v>81</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y141" s="2"/>
       <c r="Z141" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>81</v>
@@ -19150,7 +19117,7 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>108</v>
+        <v>303</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19162,7 +19129,7 @@
         <v>81</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>81</v>
@@ -19171,7 +19138,7 @@
         <v>81</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>81</v>
+        <v>304</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>81</v>
@@ -19182,21 +19149,21 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>81</v>
@@ -19205,21 +19172,21 @@
         <v>81</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>112</v>
+        <v>307</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O142" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N142" s="2"/>
+      <c r="O142" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>81</v>
       </c>
@@ -19255,31 +19222,31 @@
         <v>81</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>118</v>
+        <v>310</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>81</v>
@@ -19288,7 +19255,7 @@
         <v>81</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>81</v>
+        <v>311</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>81</v>
@@ -19299,10 +19266,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19313,7 +19280,7 @@
         <v>79</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>81</v>
@@ -19325,19 +19292,19 @@
         <v>92</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>144</v>
+        <v>314</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>243</v>
+        <v>315</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>244</v>
+        <v>316</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>245</v>
+        <v>317</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>246</v>
+        <v>318</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>81</v>
@@ -19374,23 +19341,25 @@
         <v>81</v>
       </c>
       <c r="AB143" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AC143" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD143" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE143" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>248</v>
+        <v>319</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>81</v>
@@ -19405,7 +19374,7 @@
         <v>81</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>249</v>
+        <v>320</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>81</v>
@@ -19416,13 +19385,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>611</v>
+        <v>594</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>274</v>
+        <v>322</v>
       </c>
       <c r="D144" t="s" s="2">
         <v>81</v>
@@ -19447,10 +19416,10 @@
         <v>144</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>275</v>
+        <v>323</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>276</v>
+        <v>324</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>245</v>
@@ -19485,7 +19454,7 @@
       </c>
       <c r="Y144" s="2"/>
       <c r="Z144" t="s" s="2">
-        <v>277</v>
+        <v>325</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>81</v>
@@ -19535,10 +19504,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>614</v>
+        <v>597</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19650,10 +19619,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19767,10 +19736,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>618</v>
+        <v>601</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19886,10 +19855,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20003,10 +19972,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>622</v>
+        <v>605</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20068,7 +20037,7 @@
       </c>
       <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>81</v>
@@ -20118,10 +20087,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>624</v>
+        <v>607</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20235,10 +20204,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>626</v>
+        <v>609</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20352,16 +20321,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="C152" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>619</v>
+      </c>
+      <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
         <v>81</v>
       </c>
@@ -20373,7 +20340,7 @@
         <v>91</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I152" t="s" s="2">
         <v>81</v>
@@ -20382,19 +20349,19 @@
         <v>92</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>323</v>
+        <v>251</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>324</v>
+        <v>252</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>81</v>
@@ -20419,11 +20386,13 @@
         <v>81</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y152" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z152" t="s" s="2">
-        <v>325</v>
+        <v>81</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>81</v>
@@ -20441,13 +20410,13 @@
         <v>81</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>81</v>
@@ -20462,7 +20431,7 @@
         <v>81</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>81</v>
@@ -20473,10 +20442,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>614</v>
+        <v>565</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20496,19 +20465,23 @@
         <v>81</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>105</v>
+        <v>566</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>106</v>
+        <v>567</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N153" s="2"/>
-      <c r="O153" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="O153" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P153" t="s" s="2">
         <v>81</v>
       </c>
@@ -20544,19 +20517,17 @@
         <v>81</v>
       </c>
       <c r="AB153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC153" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="AC153" s="2"/>
       <c r="AD153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE153" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>108</v>
+        <v>565</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -20568,41 +20539,43 @@
         <v>81</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>81</v>
+        <v>570</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO153" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="C154" s="2"/>
+        <v>565</v>
+      </c>
+      <c r="C154" t="s" s="2">
+        <v>623</v>
+      </c>
       <c r="D154" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>81</v>
@@ -20611,21 +20584,23 @@
         <v>81</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>111</v>
+        <v>384</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>112</v>
+        <v>567</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>113</v>
+        <v>568</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O154" s="2"/>
+        <v>569</v>
+      </c>
+      <c r="O154" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P154" t="s" s="2">
         <v>81</v>
       </c>
@@ -20661,54 +20636,54 @@
         <v>81</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>118</v>
+        <v>565</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI154" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>81</v>
+        <v>570</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20728,23 +20703,19 @@
         <v>81</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>284</v>
+        <v>106</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N155" s="2"/>
+      <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>81</v>
       </c>
@@ -20792,7 +20763,7 @@
         <v>81</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>288</v>
+        <v>108</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -20804,7 +20775,7 @@
         <v>81</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK155" t="s" s="2">
         <v>81</v>
@@ -20813,7 +20784,7 @@
         <v>81</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>81</v>
@@ -20824,21 +20795,21 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>81</v>
@@ -20847,19 +20818,19 @@
         <v>81</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>292</v>
+        <v>112</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>293</v>
+        <v>113</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>294</v>
+        <v>114</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -20897,31 +20868,31 @@
         <v>81</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC156" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD156" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>295</v>
+        <v>118</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>81</v>
@@ -20930,7 +20901,7 @@
         <v>81</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>296</v>
+        <v>81</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>81</v>
@@ -20939,12 +20910,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="157" hidden="true">
+    <row r="157">
       <c r="A157" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20958,7 +20929,7 @@
         <v>91</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>81</v>
@@ -20967,17 +20938,19 @@
         <v>92</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>166</v>
+        <v>396</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>299</v>
+        <v>397</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N157" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N157" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="O157" t="s" s="2">
-        <v>301</v>
+        <v>400</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>81</v>
@@ -21002,11 +20975,13 @@
         <v>81</v>
       </c>
       <c r="X157" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y157" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y157" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z157" t="s" s="2">
-        <v>331</v>
+        <v>81</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>81</v>
@@ -21024,7 +20999,7 @@
         <v>81</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>303</v>
+        <v>401</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21045,7 +21020,7 @@
         <v>81</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>304</v>
+        <v>402</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>81</v>
@@ -21056,10 +21031,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21076,28 +21051,30 @@
         <v>81</v>
       </c>
       <c r="I158" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J158" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>307</v>
+        <v>404</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>308</v>
+        <v>405</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>309</v>
+        <v>406</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q158" s="2"/>
+      <c r="Q158" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="R158" t="s" s="2">
         <v>81</v>
       </c>
@@ -21117,13 +21094,13 @@
         <v>81</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>81</v>
+        <v>408</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>81</v>
+        <v>409</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>81</v>
@@ -21141,7 +21118,7 @@
         <v>81</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>310</v>
+        <v>410</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21162,7 +21139,7 @@
         <v>81</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>311</v>
+        <v>411</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>81</v>
@@ -21171,12 +21148,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="159" hidden="true">
+    <row r="159">
       <c r="A159" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21190,7 +21167,7 @@
         <v>91</v>
       </c>
       <c r="H159" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I159" t="s" s="2">
         <v>81</v>
@@ -21199,19 +21176,17 @@
         <v>92</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>314</v>
+        <v>105</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>315</v>
+        <v>413</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>318</v>
+        <v>415</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>81</v>
@@ -21221,7 +21196,7 @@
         <v>81</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>81</v>
+        <v>676</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>81</v>
@@ -21260,7 +21235,7 @@
         <v>81</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>319</v>
+        <v>417</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21281,7 +21256,7 @@
         <v>81</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>320</v>
+        <v>418</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>81</v>
@@ -21290,12 +21265,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="160" hidden="true">
+    <row r="160">
       <c r="A160" t="s" s="2">
         <v>677</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21309,7 +21284,7 @@
         <v>91</v>
       </c>
       <c r="H160" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I160" t="s" s="2">
         <v>81</v>
@@ -21318,19 +21293,17 @@
         <v>92</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>251</v>
+        <v>420</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>254</v>
+        <v>422</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>81</v>
@@ -21340,7 +21313,7 @@
         <v>81</v>
       </c>
       <c r="S160" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="T160" t="s" s="2">
         <v>81</v>
@@ -21379,7 +21352,7 @@
         <v>81</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>255</v>
+        <v>424</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -21388,7 +21361,7 @@
         <v>91</v>
       </c>
       <c r="AI160" t="s" s="2">
-        <v>81</v>
+        <v>425</v>
       </c>
       <c r="AJ160" t="s" s="2">
         <v>103</v>
@@ -21400,7 +21373,7 @@
         <v>81</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>256</v>
+        <v>418</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>81</v>
@@ -21409,12 +21382,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="161" hidden="true">
+    <row r="161">
       <c r="A161" t="s" s="2">
         <v>678</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>565</v>
+        <v>637</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21428,7 +21401,7 @@
         <v>91</v>
       </c>
       <c r="H161" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I161" t="s" s="2">
         <v>81</v>
@@ -21437,19 +21410,19 @@
         <v>92</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>566</v>
+        <v>166</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>567</v>
+        <v>427</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>568</v>
+        <v>428</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>569</v>
+        <v>429</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>388</v>
+        <v>430</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>81</v>
@@ -21459,7 +21432,7 @@
         <v>81</v>
       </c>
       <c r="S161" t="s" s="2">
-        <v>81</v>
+        <v>676</v>
       </c>
       <c r="T161" t="s" s="2">
         <v>81</v>
@@ -21486,17 +21459,19 @@
         <v>81</v>
       </c>
       <c r="AB161" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AC161" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC161" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD161" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE161" t="s" s="2">
-        <v>638</v>
+        <v>81</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>565</v>
+        <v>431</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -21514,16 +21489,16 @@
         <v>81</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>571</v>
+        <v>81</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
     </row>
     <row r="162" hidden="true">
@@ -21531,11 +21506,9 @@
         <v>679</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="C162" t="s" s="2">
-        <v>573</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
         <v>81</v>
       </c>
@@ -21553,22 +21526,22 @@
         <v>81</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>384</v>
+        <v>232</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>81</v>
@@ -21593,13 +21566,13 @@
         <v>81</v>
       </c>
       <c r="X162" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>81</v>
@@ -21617,7 +21590,7 @@
         <v>81</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -21626,7 +21599,7 @@
         <v>91</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>103</v>
@@ -21635,16 +21608,16 @@
         <v>81</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>571</v>
+        <v>81</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
     </row>
     <row r="163" hidden="true">
@@ -21656,14 +21629,14 @@
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>81</v>
@@ -21675,16 +21648,20 @@
         <v>81</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>106</v>
+        <v>576</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N163" s="2"/>
-      <c r="O163" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="N163" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O163" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P163" t="s" s="2">
         <v>81</v>
       </c>
@@ -21708,13 +21685,13 @@
         <v>81</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>81</v>
@@ -21732,34 +21709,34 @@
         <v>81</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>108</v>
+        <v>575</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH163" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>81</v>
+        <v>450</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>81</v>
+        <v>451</v>
       </c>
     </row>
     <row r="164" hidden="true">
@@ -21767,11 +21744,11 @@
         <v>681</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
@@ -21790,18 +21767,20 @@
         <v>81</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>112</v>
+        <v>579</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>113</v>
+        <v>580</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O164" s="2"/>
+        <v>496</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>497</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>81</v>
       </c>
@@ -21837,19 +21816,19 @@
         <v>81</v>
       </c>
       <c r="AB164" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC164" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD164" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE164" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>118</v>
+        <v>578</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -21861,7 +21840,7 @@
         <v>81</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK164" t="s" s="2">
         <v>81</v>
@@ -21870,7 +21849,7 @@
         <v>81</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>81</v>
+        <v>499</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>81</v>
@@ -21879,14 +21858,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="165" hidden="true">
+    <row r="165">
       <c r="A165" t="s" s="2">
         <v>682</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="C165" s="2"/>
+        <v>551</v>
+      </c>
+      <c r="C165" t="s" s="2">
+        <v>683</v>
+      </c>
       <c r="D165" t="s" s="2">
         <v>81</v>
       </c>
@@ -21898,7 +21879,7 @@
         <v>91</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>81</v>
@@ -21907,19 +21888,19 @@
         <v>92</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>396</v>
+        <v>493</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>397</v>
+        <v>684</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>398</v>
+        <v>685</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>399</v>
+        <v>554</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>400</v>
+        <v>555</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>81</v>
@@ -21968,13 +21949,13 @@
         <v>81</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>401</v>
+        <v>551</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH165" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI165" t="s" s="2">
         <v>81</v>
@@ -21989,7 +21970,7 @@
         <v>81</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>402</v>
+        <v>556</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>81</v>
@@ -22000,10 +21981,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>581</v>
+        <v>557</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22020,30 +22001,26 @@
         <v>81</v>
       </c>
       <c r="I166" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J166" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>404</v>
+        <v>106</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>405</v>
+        <v>107</v>
       </c>
       <c r="N166" s="2"/>
-      <c r="O166" t="s" s="2">
-        <v>406</v>
-      </c>
+      <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q166" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="Q166" s="2"/>
       <c r="R166" t="s" s="2">
         <v>81</v>
       </c>
@@ -22063,13 +22040,13 @@
         <v>81</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>408</v>
+        <v>81</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>409</v>
+        <v>81</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>81</v>
@@ -22087,7 +22064,7 @@
         <v>81</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>410</v>
+        <v>108</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -22099,7 +22076,7 @@
         <v>81</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>81</v>
@@ -22108,7 +22085,7 @@
         <v>81</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>81</v>
@@ -22119,21 +22096,21 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>583</v>
+        <v>558</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>81</v>
@@ -22142,21 +22119,21 @@
         <v>81</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>413</v>
+        <v>112</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N167" s="2"/>
-      <c r="O167" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N167" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>81</v>
       </c>
@@ -22165,7 +22142,7 @@
         <v>81</v>
       </c>
       <c r="S167" t="s" s="2">
-        <v>685</v>
+        <v>81</v>
       </c>
       <c r="T167" t="s" s="2">
         <v>81</v>
@@ -22204,19 +22181,19 @@
         <v>81</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>417</v>
+        <v>118</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI167" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>81</v>
@@ -22225,7 +22202,7 @@
         <v>81</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>81</v>
@@ -22236,43 +22213,45 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>585</v>
+        <v>559</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>81</v>
+        <v>503</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I168" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J168" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>420</v>
+        <v>504</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N168" s="2"/>
+        <v>505</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O168" t="s" s="2">
-        <v>422</v>
+        <v>194</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>81</v>
@@ -22282,7 +22261,7 @@
         <v>81</v>
       </c>
       <c r="S168" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="T168" t="s" s="2">
         <v>81</v>
@@ -22321,19 +22300,19 @@
         <v>81</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>424</v>
+        <v>506</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>81</v>
@@ -22342,7 +22321,7 @@
         <v>81</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>81</v>
@@ -22353,10 +22332,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>587</v>
+        <v>560</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22364,7 +22343,7 @@
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G169" t="s" s="2">
         <v>91</v>
@@ -22379,19 +22358,19 @@
         <v>92</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>427</v>
+        <v>561</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>428</v>
+        <v>562</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>429</v>
+        <v>563</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>430</v>
+        <v>261</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>81</v>
@@ -22401,7 +22380,7 @@
         <v>81</v>
       </c>
       <c r="S169" t="s" s="2">
-        <v>685</v>
+        <v>81</v>
       </c>
       <c r="T169" t="s" s="2">
         <v>81</v>
@@ -22416,13 +22395,13 @@
         <v>81</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>81</v>
@@ -22440,10 +22419,10 @@
         <v>81</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>431</v>
+        <v>560</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH169" t="s" s="2">
         <v>91</v>
@@ -22458,13 +22437,13 @@
         <v>81</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>81</v>
+        <v>564</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>418</v>
+        <v>266</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>81</v>
@@ -22472,10 +22451,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22498,20 +22477,16 @@
         <v>81</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>589</v>
+        <v>106</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N170" s="2"/>
+      <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
         <v>81</v>
       </c>
@@ -22535,13 +22510,13 @@
         <v>81</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>81</v>
@@ -22559,7 +22534,7 @@
         <v>81</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>588</v>
+        <v>108</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
@@ -22568,10 +22543,10 @@
         <v>91</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>439</v>
+        <v>81</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK170" t="s" s="2">
         <v>81</v>
@@ -22580,7 +22555,7 @@
         <v>81</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>81</v>
@@ -22591,14 +22566,14 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>592</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>442</v>
+        <v>110</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
@@ -22617,20 +22592,18 @@
         <v>81</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>593</v>
+        <v>112</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>594</v>
+        <v>113</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O171" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
         <v>81</v>
       </c>
@@ -22654,31 +22627,31 @@
         <v>81</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB171" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC171" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE171" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>592</v>
+        <v>118</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>79</v>
@@ -22690,30 +22663,30 @@
         <v>81</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>449</v>
+        <v>81</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>450</v>
+        <v>81</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22733,22 +22706,22 @@
         <v>81</v>
       </c>
       <c r="J172" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>596</v>
+        <v>243</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>597</v>
+        <v>244</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>496</v>
+        <v>245</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>497</v>
+        <v>246</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>81</v>
@@ -22785,19 +22758,17 @@
         <v>81</v>
       </c>
       <c r="AB172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC172" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="AC172" s="2"/>
       <c r="AD172" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE172" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>595</v>
+        <v>248</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -22818,7 +22789,7 @@
         <v>81</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>499</v>
+        <v>249</v>
       </c>
       <c r="AN172" t="s" s="2">
         <v>81</v>
@@ -22829,13 +22800,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>551</v>
+        <v>594</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>692</v>
+        <v>274</v>
       </c>
       <c r="D173" t="s" s="2">
         <v>81</v>
@@ -22857,19 +22828,19 @@
         <v>92</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>493</v>
+        <v>144</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>693</v>
+        <v>275</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>694</v>
+        <v>276</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>554</v>
+        <v>245</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>555</v>
+        <v>246</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>81</v>
@@ -22879,7 +22850,7 @@
         <v>81</v>
       </c>
       <c r="S173" t="s" s="2">
-        <v>81</v>
+        <v>694</v>
       </c>
       <c r="T173" t="s" s="2">
         <v>81</v>
@@ -22918,7 +22889,7 @@
         <v>81</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>551</v>
+        <v>248</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>79</v>
@@ -22939,7 +22910,7 @@
         <v>81</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>556</v>
+        <v>249</v>
       </c>
       <c r="AN173" t="s" s="2">
         <v>81</v>
@@ -22953,7 +22924,7 @@
         <v>695</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>557</v>
+        <v>597</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23068,7 +23039,7 @@
         <v>696</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>558</v>
+        <v>599</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23138,16 +23109,16 @@
         <v>81</v>
       </c>
       <c r="AB175" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC175" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD175" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE175" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF175" t="s" s="2">
         <v>118</v>
@@ -23185,42 +23156,42 @@
         <v>697</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>559</v>
+        <v>601</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>503</v>
+        <v>81</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I176" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J176" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>504</v>
+        <v>284</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>505</v>
+        <v>285</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>114</v>
+        <v>286</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>194</v>
+        <v>287</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>81</v>
@@ -23269,19 +23240,19 @@
         <v>81</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>506</v>
+        <v>288</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>81</v>
@@ -23290,7 +23261,7 @@
         <v>81</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>81</v>
+        <v>289</v>
       </c>
       <c r="AN176" t="s" s="2">
         <v>81</v>
@@ -23304,7 +23275,7 @@
         <v>698</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>560</v>
+        <v>603</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23312,7 +23283,7 @@
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G177" t="s" s="2">
         <v>91</v>
@@ -23327,20 +23298,18 @@
         <v>92</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>561</v>
+        <v>292</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>562</v>
+        <v>293</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>81</v>
       </c>
@@ -23364,13 +23333,13 @@
         <v>81</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>81</v>
@@ -23388,10 +23357,10 @@
         <v>81</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>560</v>
+        <v>295</v>
       </c>
       <c r="AG177" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH177" t="s" s="2">
         <v>91</v>
@@ -23406,13 +23375,13 @@
         <v>81</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>564</v>
+        <v>81</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>81</v>
@@ -23423,7 +23392,7 @@
         <v>699</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23443,19 +23412,21 @@
         <v>81</v>
       </c>
       <c r="J178" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>106</v>
+        <v>299</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>107</v>
+        <v>300</v>
       </c>
       <c r="N178" s="2"/>
-      <c r="O178" s="2"/>
+      <c r="O178" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P178" t="s" s="2">
         <v>81</v>
       </c>
@@ -23479,13 +23450,11 @@
         <v>81</v>
       </c>
       <c r="X178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y178" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y178" s="2"/>
       <c r="Z178" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>81</v>
@@ -23503,7 +23472,7 @@
         <v>81</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>108</v>
+        <v>303</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -23515,7 +23484,7 @@
         <v>81</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>81</v>
@@ -23524,7 +23493,7 @@
         <v>81</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>81</v>
+        <v>304</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>81</v>
@@ -23538,18 +23507,18 @@
         <v>700</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H179" t="s" s="2">
         <v>81</v>
@@ -23558,21 +23527,21 @@
         <v>81</v>
       </c>
       <c r="J179" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>112</v>
+        <v>307</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O179" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N179" s="2"/>
+      <c r="O179" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P179" t="s" s="2">
         <v>81</v>
       </c>
@@ -23608,31 +23577,31 @@
         <v>81</v>
       </c>
       <c r="AB179" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC179" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD179" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE179" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>118</v>
+        <v>310</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH179" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI179" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>81</v>
@@ -23641,7 +23610,7 @@
         <v>81</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>81</v>
+        <v>311</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>81</v>
@@ -23655,7 +23624,7 @@
         <v>701</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23666,7 +23635,7 @@
         <v>79</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H180" t="s" s="2">
         <v>81</v>
@@ -23678,19 +23647,19 @@
         <v>92</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>144</v>
+        <v>314</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>243</v>
+        <v>315</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>244</v>
+        <v>316</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>245</v>
+        <v>317</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>246</v>
+        <v>318</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>81</v>
@@ -23727,23 +23696,25 @@
         <v>81</v>
       </c>
       <c r="AB180" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AC180" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC180" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD180" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE180" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>248</v>
+        <v>319</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI180" t="s" s="2">
         <v>81</v>
@@ -23758,7 +23729,7 @@
         <v>81</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>249</v>
+        <v>320</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>81</v>
@@ -23767,16 +23738,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
         <v>702</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="C181" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>619</v>
+      </c>
+      <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
         <v>81</v>
       </c>
@@ -23788,7 +23757,7 @@
         <v>91</v>
       </c>
       <c r="H181" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I181" t="s" s="2">
         <v>81</v>
@@ -23797,19 +23766,19 @@
         <v>92</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>81</v>
@@ -23819,7 +23788,7 @@
         <v>81</v>
       </c>
       <c r="S181" t="s" s="2">
-        <v>703</v>
+        <v>81</v>
       </c>
       <c r="T181" t="s" s="2">
         <v>81</v>
@@ -23858,13 +23827,13 @@
         <v>81</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI181" t="s" s="2">
         <v>81</v>
@@ -23879,7 +23848,7 @@
         <v>81</v>
       </c>
       <c r="AM181" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AN181" t="s" s="2">
         <v>81</v>
@@ -23890,10 +23859,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>614</v>
+        <v>565</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23913,19 +23882,23 @@
         <v>81</v>
       </c>
       <c r="J182" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>105</v>
+        <v>566</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>106</v>
+        <v>567</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N182" s="2"/>
-      <c r="O182" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="O182" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P182" t="s" s="2">
         <v>81</v>
       </c>
@@ -23973,7 +23946,7 @@
         <v>81</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>108</v>
+        <v>565</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>79</v>
@@ -23985,41 +23958,41 @@
         <v>81</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK182" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>81</v>
+        <v>570</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="AN182" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO182" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>616</v>
+        <v>571</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G183" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H183" t="s" s="2">
         <v>81</v>
@@ -24031,18 +24004,20 @@
         <v>81</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>111</v>
+        <v>232</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>112</v>
+        <v>572</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>113</v>
+        <v>573</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O183" s="2"/>
+        <v>574</v>
+      </c>
+      <c r="O183" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P183" t="s" s="2">
         <v>81</v>
       </c>
@@ -24066,43 +24041,43 @@
         <v>81</v>
       </c>
       <c r="X183" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y183" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="Z183" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB183" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC183" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD183" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE183" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>118</v>
+        <v>571</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH183" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI183" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK183" t="s" s="2">
         <v>81</v>
@@ -24111,7 +24086,7 @@
         <v>81</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>81</v>
+        <v>440</v>
       </c>
       <c r="AN183" t="s" s="2">
         <v>81</v>
@@ -24122,21 +24097,21 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>618</v>
+        <v>575</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="E184" s="2"/>
       <c r="F184" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>81</v>
@@ -24145,22 +24120,22 @@
         <v>81</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>132</v>
+        <v>232</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>284</v>
+        <v>576</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>285</v>
+        <v>577</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>286</v>
+        <v>445</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>287</v>
+        <v>446</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>81</v>
@@ -24185,13 +24160,13 @@
         <v>81</v>
       </c>
       <c r="X184" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>81</v>
@@ -24209,13 +24184,13 @@
         <v>81</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>288</v>
+        <v>575</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH184" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI184" t="s" s="2">
         <v>81</v>
@@ -24227,24 +24202,24 @@
         <v>81</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>289</v>
+        <v>450</v>
       </c>
       <c r="AN184" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>81</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>620</v>
+        <v>578</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24255,7 +24230,7 @@
         <v>79</v>
       </c>
       <c r="G185" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H185" t="s" s="2">
         <v>81</v>
@@ -24264,21 +24239,23 @@
         <v>81</v>
       </c>
       <c r="J185" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>292</v>
+        <v>579</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>293</v>
+        <v>580</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O185" s="2"/>
+        <v>496</v>
+      </c>
+      <c r="O185" t="s" s="2">
+        <v>497</v>
+      </c>
       <c r="P185" t="s" s="2">
         <v>81</v>
       </c>
@@ -24326,13 +24303,13 @@
         <v>81</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>295</v>
+        <v>578</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH185" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI185" t="s" s="2">
         <v>81</v>
@@ -24347,963 +24324,17 @@
         <v>81</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>296</v>
+        <v>499</v>
       </c>
       <c r="AN185" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO185" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="186" hidden="true">
-      <c r="A186" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="B186" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C186" s="2"/>
-      <c r="D186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E186" s="2"/>
-      <c r="F186" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G186" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J186" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K186" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L186" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="M186" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N186" s="2"/>
-      <c r="O186" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="P186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q186" s="2"/>
-      <c r="R186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X186" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y186" s="2"/>
-      <c r="Z186" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AA186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF186" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AG186" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH186" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ186" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM186" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AN186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO186" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="187" hidden="true">
-      <c r="A187" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="B187" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="C187" s="2"/>
-      <c r="D187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E187" s="2"/>
-      <c r="F187" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G187" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J187" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K187" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L187" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="M187" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N187" s="2"/>
-      <c r="O187" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="P187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q187" s="2"/>
-      <c r="R187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF187" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AG187" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH187" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ187" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM187" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="AN187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO187" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="188" hidden="true">
-      <c r="A188" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="B188" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C188" s="2"/>
-      <c r="D188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E188" s="2"/>
-      <c r="F188" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G188" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J188" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K188" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="L188" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="M188" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O188" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="P188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q188" s="2"/>
-      <c r="R188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF188" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AG188" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH188" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ188" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM188" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="AN188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO188" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="189" hidden="true">
-      <c r="A189" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="B189" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="C189" s="2"/>
-      <c r="D189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E189" s="2"/>
-      <c r="F189" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G189" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J189" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K189" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L189" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="M189" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N189" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O189" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="P189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q189" s="2"/>
-      <c r="R189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF189" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AG189" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH189" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ189" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM189" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AN189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO189" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="190" hidden="true">
-      <c r="A190" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="B190" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="C190" s="2"/>
-      <c r="D190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E190" s="2"/>
-      <c r="F190" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G190" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J190" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K190" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="L190" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="M190" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="N190" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="O190" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="P190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q190" s="2"/>
-      <c r="R190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF190" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="AG190" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH190" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ190" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL190" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AM190" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AN190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO190" t="s" s="2">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="191" hidden="true">
-      <c r="A191" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="B191" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="C191" s="2"/>
-      <c r="D191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E191" s="2"/>
-      <c r="F191" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G191" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K191" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L191" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="M191" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N191" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="P191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q191" s="2"/>
-      <c r="R191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X191" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="Y191" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="Z191" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AA191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF191" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="AG191" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH191" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI191" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AJ191" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM191" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AN191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO191" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="192" hidden="true">
-      <c r="A192" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="B192" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="C192" s="2"/>
-      <c r="D192" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="E192" s="2"/>
-      <c r="F192" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G192" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K192" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L192" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="M192" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O192" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="P192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q192" s="2"/>
-      <c r="R192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X192" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="Y192" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="Z192" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AA192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF192" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="AG192" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH192" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ192" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL192" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AM192" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AN192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO192" t="s" s="2">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="193" hidden="true">
-      <c r="A193" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="B193" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="C193" s="2"/>
-      <c r="D193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E193" s="2"/>
-      <c r="F193" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G193" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L193" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="M193" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N193" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="O193" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="P193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q193" s="2"/>
-      <c r="R193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF193" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AG193" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH193" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ193" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM193" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AN193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO193" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO193">
+  <autoFilter ref="A1:AO185">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -25313,7 +24344,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI192">
+  <conditionalFormatting sqref="A2:AI184">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-fvc.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-fvc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-fvc.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-fvc.xlsx
@@ -2173,7 +2173,7 @@
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
-  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
   &lt;code value="1078210003"/&gt;
   &lt;display value="Z-score calculation technique (qualifier value)"/&gt;
 &lt;/valueCoding&gt;</t>
